--- a/summary/train_data_after_stand_summary.xlsx
+++ b/summary/train_data_after_stand_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,16 +480,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9237292282108067</v>
+        <v>-3.751176719973921</v>
       </c>
       <c r="C3" t="n">
-        <v>20.51827315777325</v>
+        <v>6.126490223054396</v>
       </c>
       <c r="D3" t="n">
-        <v>-5.840077280220001e-17</v>
+        <v>-1.944259061206575e-15</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1040633490653693</v>
+        <v>0.08878817230528258</v>
       </c>
       <c r="F3" t="n">
         <v>1.000342641778087</v>
@@ -505,22 +505,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.5707501337786359</v>
+        <v>-0.8068408258386879</v>
       </c>
       <c r="C4" t="n">
-        <v>8.285201088776468</v>
+        <v>2.00091404783834</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.893384853480001e-17</v>
+        <v>4.623394513507501e-17</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5707501337786359</v>
+        <v>-0.8068408258386879</v>
       </c>
       <c r="F4" t="n">
         <v>1.000342641778087</v>
       </c>
       <c r="G4" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000685400959562</v>
       </c>
     </row>
     <row r="5">
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.9730181828073765</v>
+        <v>-1.4141397865663</v>
       </c>
       <c r="C5" t="n">
-        <v>11.40575292712178</v>
+        <v>1.474006695898278</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.433365533425001e-17</v>
+        <v>1.703355873397501e-17</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1319021798559533</v>
+        <v>0.5757927687657827</v>
       </c>
       <c r="F5" t="n">
         <v>1.000342641778087</v>
@@ -555,16 +555,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.2886528311122454</v>
+        <v>-0.3553424078009089</v>
       </c>
       <c r="C6" t="n">
-        <v>8.851637899984492</v>
+        <v>3.600612433231367</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.406711746795001e-17</v>
+        <v>9.733462133700002e-17</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2886528311122454</v>
+        <v>-0.3553424078009089</v>
       </c>
       <c r="F6" t="n">
         <v>1.000342641778087</v>
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.28417561989079</v>
+        <v>-3.047600483023416</v>
       </c>
       <c r="C7" t="n">
-        <v>4.004295000518199</v>
+        <v>1.137510739512567</v>
       </c>
       <c r="D7" t="n">
-        <v>-6.600504009415314e-17</v>
+        <v>5.621074382211751e-16</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2031633248371547</v>
+        <v>0.2817943942669537</v>
       </c>
       <c r="F7" t="n">
         <v>1.000342641778087</v>
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2.411166932760057</v>
+        <v>-5.894038092795351</v>
       </c>
       <c r="C8" t="n">
-        <v>11.52094922925559</v>
+        <v>1.717673474673863</v>
       </c>
       <c r="D8" t="n">
-        <v>2.45769918875925e-16</v>
+        <v>1.107181317708375e-16</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.150333352622821</v>
+        <v>0.1306770239551147</v>
       </c>
       <c r="F8" t="n">
         <v>1.000342641778087</v>
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-2.14417208020907</v>
+        <v>-3.763749271224468</v>
       </c>
       <c r="C9" t="n">
-        <v>9.132681280322796</v>
+        <v>4.554909481510379</v>
       </c>
       <c r="D9" t="n">
-        <v>6.509252801911877e-17</v>
+        <v>1.424127178436982e-15</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1956932870744915</v>
+        <v>-0.05154533417364471</v>
       </c>
       <c r="F9" t="n">
         <v>1.000342641778087</v>
       </c>
       <c r="G9" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000685400959562</v>
       </c>
     </row>
     <row r="10">
@@ -655,22 +655,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.7951632272572445</v>
+        <v>-0.8701173641387884</v>
       </c>
       <c r="C10" t="n">
-        <v>3.936962759169894</v>
+        <v>1.448517014256568</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.82502415006875e-17</v>
+        <v>1.533020286057751e-16</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7951632272572445</v>
+        <v>-0.8701173641387884</v>
       </c>
       <c r="F10" t="n">
         <v>1.000342641778087</v>
       </c>
       <c r="G10" t="n">
-        <v>1.000685400959562</v>
+        <v>1.000685400959561</v>
       </c>
     </row>
     <row r="11">
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1202417237346725</v>
+        <v>-0.1336023189084742</v>
       </c>
       <c r="C11" t="n">
-        <v>11.64774940778996</v>
+        <v>8.367141663773715</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2166827667125e-17</v>
+        <v>-5.718409003548751e-17</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1202417237346725</v>
+        <v>-0.1336023189084742</v>
       </c>
       <c r="F11" t="n">
         <v>1.000342641778087</v>
@@ -705,16 +705,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-2.249120147460856</v>
+        <v>-4.365035778520943</v>
       </c>
       <c r="C12" t="n">
-        <v>7.855574356961303</v>
+        <v>4.110759944598887</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.277516905048125e-16</v>
+        <v>7.871937500629877e-16</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.09797003630843711</v>
+        <v>0.06332373124701897</v>
       </c>
       <c r="F12" t="n">
         <v>1.000342641778087</v>
@@ -755,16 +755,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2410610357992968</v>
+        <v>-0.2429231735496986</v>
       </c>
       <c r="C14" t="n">
-        <v>8.138679732461972</v>
+        <v>6.515952899906281</v>
       </c>
       <c r="D14" t="n">
-        <v>2.433365533425001e-17</v>
+        <v>7.543433153617502e-17</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2410610357992968</v>
+        <v>-0.2429231735496986</v>
       </c>
       <c r="F14" t="n">
         <v>1.000342641778087</v>
@@ -855,22 +855,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-4.751486354069578</v>
+        <v>-7.975078122202384</v>
       </c>
       <c r="C18" t="n">
-        <v>8.868611964533009</v>
+        <v>7.559863578251679</v>
       </c>
       <c r="D18" t="n">
-        <v>4.501726236836251e-16</v>
+        <v>-7.458265359947627e-16</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2114535812020489</v>
+        <v>-0.2076072719753528</v>
       </c>
       <c r="F18" t="n">
         <v>1.000342641778087</v>
       </c>
       <c r="G18" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000685400959562</v>
       </c>
     </row>
     <row r="19">
@@ -980,22 +980,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.7521758378613592</v>
+        <v>-0.9467014684878265</v>
       </c>
       <c r="C23" t="n">
-        <v>6.087634999939538</v>
+        <v>1.655682038412637</v>
       </c>
       <c r="D23" t="n">
-        <v>5.596740726877502e-17</v>
+        <v>1.460019320055e-17</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7521758378613592</v>
+        <v>-0.9467014684878265</v>
       </c>
       <c r="F23" t="n">
         <v>1.000342641778087</v>
       </c>
       <c r="G23" t="n">
-        <v>1.000685400959562</v>
+        <v>1.000685400959561</v>
       </c>
     </row>
     <row r="24">
@@ -1005,22 +1005,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.704483250333654</v>
+        <v>-1.072916474962699</v>
       </c>
       <c r="C24" t="n">
-        <v>7.554198174442678</v>
+        <v>1.857985397808924</v>
       </c>
       <c r="D24" t="n">
-        <v>3.041706916781251e-17</v>
+        <v>-2.104861186412626e-16</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3270298031318107</v>
+        <v>0.4413151134872422</v>
       </c>
       <c r="F24" t="n">
         <v>1.000342641778087</v>
       </c>
       <c r="G24" t="n">
-        <v>1.000685400959562</v>
+        <v>1.000685400959561</v>
       </c>
     </row>
     <row r="25">
@@ -1030,16 +1030,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.3593249004055313</v>
+        <v>-0.4042442108783149</v>
       </c>
       <c r="C25" t="n">
-        <v>8.67530910373841</v>
+        <v>3.253174886581788</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.311697256753751e-17</v>
+        <v>-2.676702086767501e-17</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3593249004055313</v>
+        <v>-0.4042442108783149</v>
       </c>
       <c r="F25" t="n">
         <v>1.000342641778087</v>
@@ -1055,16 +1055,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1163392861482226</v>
+        <v>-0.1285214274886148</v>
       </c>
       <c r="C26" t="n">
-        <v>17.21723278103011</v>
+        <v>9.22041485120967</v>
       </c>
       <c r="D26" t="n">
-        <v>4.866731066850001e-18</v>
+        <v>-4.866731066850001e-18</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1163392861482226</v>
+        <v>-0.1285214274886148</v>
       </c>
       <c r="F26" t="n">
         <v>1.000342641778087</v>
@@ -1080,22 +1080,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2702083542015609</v>
+        <v>-0.2927694190084836</v>
       </c>
       <c r="C27" t="n">
-        <v>8.341461781978069</v>
+        <v>4.110032180254794</v>
       </c>
       <c r="D27" t="n">
-        <v>5.475072450206251e-17</v>
+        <v>-4.440892098500626e-17</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2702083542015609</v>
+        <v>-0.2927694190084836</v>
       </c>
       <c r="F27" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000342641778086</v>
       </c>
       <c r="G27" t="n">
-        <v>1.000685400959562</v>
+        <v>1.000685400959561</v>
       </c>
     </row>
     <row r="28">
@@ -1105,22 +1105,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.06869174753820707</v>
+        <v>-0.06939258050999438</v>
       </c>
       <c r="C28" t="n">
-        <v>18.30618018331268</v>
+        <v>14.99281765578674</v>
       </c>
       <c r="D28" t="n">
-        <v>1.946692426740001e-17</v>
+        <v>-2.92003864011e-17</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.06869174753820707</v>
+        <v>-0.06939258050999438</v>
       </c>
       <c r="F28" t="n">
         <v>1.000342641778087</v>
       </c>
       <c r="G28" t="n">
-        <v>1.000685400959562</v>
+        <v>1.000685400959561</v>
       </c>
     </row>
     <row r="29">
@@ -1130,19 +1130,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.08768781151769862</v>
+        <v>-0.1904814736846831</v>
       </c>
       <c r="C29" t="n">
-        <v>31.16526797399778</v>
+        <v>7.682057447498138</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.676702086767501e-17</v>
+        <v>-3.406711746795001e-17</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.08768781151769862</v>
+        <v>-0.1904814736846831</v>
       </c>
       <c r="F29" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000342641778086</v>
       </c>
       <c r="G29" t="n">
         <v>1.000685400959561</v>
@@ -1245,6 +1245,181 @@
         <v>1.000342641778087</v>
       </c>
       <c r="G33" t="n">
+        <v>1.000685400959561</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TotalArea</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-6.361593505175152</v>
+      </c>
+      <c r="C34" t="n">
+        <v>5.00544702298796</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-1.418043764603419e-15</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.03446994549377981</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.000342641778087</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.000685400959561</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TotalBaths</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-1.541932106739068</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4.826443779651425</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.567200637763375e-16</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.2682569294609691</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.000342641778087</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.000685400959562</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TotalPorchArea</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-2.048330799186041</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.294621051308918</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.070680834707e-16</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.412810967265625</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.000342641778087</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.000685400959561</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AvgRoomSize</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-3.363038893116097</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3.863104357408187</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-1.87369146073725e-15</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.006981842319383289</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.000342641778087</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.000685400959561</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LotUtilization</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-1.793919398933742</v>
+      </c>
+      <c r="C38" t="n">
+        <v>5.912391734020543</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-6.083413833562501e-17</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.2048290518243997</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.000342641778087</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.000685400959561</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Qual_x_Area</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-6.271177421017662</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3.668021063152571</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3.248542987122376e-16</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.07017578565671938</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.000342641778087</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.000685400959561</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TotalQualCond</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-5.714683694835959</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4.326976433010307</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-2.652368431433251e-16</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.1921752038971382</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.000342641778087</v>
+      </c>
+      <c r="G40" t="n">
         <v>1.000685400959561</v>
       </c>
     </row>

--- a/summary/train_data_after_stand_summary.xlsx
+++ b/summary/train_data_after_stand_summary.xlsx
@@ -455,22 +455,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.6628930854346</v>
+        <v>-1.655820968246297</v>
       </c>
       <c r="C2" t="n">
-        <v>7.369662271535608</v>
+        <v>7.314728562071187</v>
       </c>
       <c r="D2" t="n">
-        <v>9.490125580357503e-17</v>
+        <v>-3.878176318896095e-17</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1551611876935887</v>
+        <v>0.1497528988783087</v>
       </c>
       <c r="F2" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G2" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029134</v>
       </c>
     </row>
     <row r="3">
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-3.751176719973921</v>
+        <v>-3.665727335552913</v>
       </c>
       <c r="C3" t="n">
-        <v>6.126490223054396</v>
+        <v>5.979552802992192</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.944259061206575e-15</v>
+        <v>1.234933008213188e-15</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08878817230528258</v>
+        <v>0.08817399678522271</v>
       </c>
       <c r="F3" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G3" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="4">
@@ -505,22 +505,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.8068408258386879</v>
+        <v>-0.814082116124212</v>
       </c>
       <c r="C4" t="n">
-        <v>2.00091404783834</v>
+        <v>1.974338220089738</v>
       </c>
       <c r="D4" t="n">
-        <v>4.623394513507501e-17</v>
+        <v>1.277516905048125e-16</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8068408258386879</v>
+        <v>-0.814082116124212</v>
       </c>
       <c r="F4" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G4" t="n">
-        <v>1.000685400959562</v>
+        <v>1.000856898029134</v>
       </c>
     </row>
     <row r="5">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.4141397865663</v>
+        <v>-1.387610692907509</v>
       </c>
       <c r="C5" t="n">
-        <v>1.474006695898278</v>
+        <v>1.48205858102279</v>
       </c>
       <c r="D5" t="n">
-        <v>1.703355873397501e-17</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5757927687657827</v>
+        <v>0.5817229259855839</v>
       </c>
       <c r="F5" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G5" t="n">
-        <v>1.000685400959562</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="6">
@@ -555,22 +555,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.3553424078009089</v>
+        <v>-0.3499719275005094</v>
       </c>
       <c r="C6" t="n">
-        <v>3.600612433231367</v>
+        <v>3.652862521617557</v>
       </c>
       <c r="D6" t="n">
-        <v>9.733462133700002e-17</v>
+        <v>-3.041706916781251e-18</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3553424078009089</v>
+        <v>-0.3499719275005094</v>
       </c>
       <c r="F6" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G6" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="7">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-3.047600483023416</v>
+        <v>-3.061597250143507</v>
       </c>
       <c r="C7" t="n">
-        <v>1.137510739512567</v>
+        <v>1.131621429392466</v>
       </c>
       <c r="D7" t="n">
-        <v>5.621074382211751e-16</v>
+        <v>1.748981477149219e-16</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2817943942669537</v>
+        <v>0.2826576451199165</v>
       </c>
       <c r="F7" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G7" t="n">
-        <v>1.000685400959562</v>
+        <v>1.000856898029134</v>
       </c>
     </row>
     <row r="8">
@@ -605,22 +605,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-5.894038092795351</v>
+        <v>-5.855128763550051</v>
       </c>
       <c r="C8" t="n">
-        <v>1.717673474673863</v>
+        <v>1.707207554756969</v>
       </c>
       <c r="D8" t="n">
-        <v>1.107181317708375e-16</v>
+        <v>1.82502415006875e-16</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1306770239551147</v>
+        <v>0.1291936526293741</v>
       </c>
       <c r="F8" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G8" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="9">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-3.763749271224468</v>
+        <v>-3.748544728592112</v>
       </c>
       <c r="C9" t="n">
-        <v>4.554909481510379</v>
+        <v>4.537684309890437</v>
       </c>
       <c r="D9" t="n">
-        <v>1.424127178436982e-15</v>
+        <v>1.592333570934985e-15</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.05154533417364471</v>
+        <v>-0.04792737315145701</v>
       </c>
       <c r="F9" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G9" t="n">
-        <v>1.000685400959562</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="10">
@@ -655,22 +655,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.8701173641387884</v>
+        <v>-0.8826071464803253</v>
       </c>
       <c r="C10" t="n">
-        <v>1.448517014256568</v>
+        <v>1.429152458629092</v>
       </c>
       <c r="D10" t="n">
-        <v>1.533020286057751e-16</v>
+        <v>-5.475072450206251e-17</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8701173641387884</v>
+        <v>-0.8826071464803253</v>
       </c>
       <c r="F10" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G10" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="11">
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1336023189084742</v>
+        <v>-0.1308461190789479</v>
       </c>
       <c r="C11" t="n">
-        <v>8.367141663773715</v>
+        <v>8.51145475180687</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.718409003548751e-17</v>
+        <v>2.129194841746875e-17</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1336023189084742</v>
+        <v>-0.1308461190789479</v>
       </c>
       <c r="F11" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G11" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029134</v>
       </c>
     </row>
     <row r="12">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-4.365035778520943</v>
+        <v>-4.32990534974626</v>
       </c>
       <c r="C12" t="n">
-        <v>4.110759944598887</v>
+        <v>4.052270416861941</v>
       </c>
       <c r="D12" t="n">
-        <v>7.871937500629877e-16</v>
+        <v>-7.102385650684221e-16</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06332373124701897</v>
+        <v>0.05358974351768461</v>
       </c>
       <c r="F12" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G12" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="13">
@@ -730,22 +730,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.8199643654586394</v>
+        <v>-0.7930957731111337</v>
       </c>
       <c r="C13" t="n">
-        <v>4.963359178355918</v>
+        <v>4.984466781943778</v>
       </c>
       <c r="D13" t="n">
-        <v>2.311697256753751e-17</v>
+        <v>-6.083413833562501e-18</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8199643654586394</v>
+        <v>-0.7930957731111337</v>
       </c>
       <c r="F13" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G13" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029134</v>
       </c>
     </row>
     <row r="14">
@@ -755,22 +755,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2429231735496986</v>
+        <v>-0.2531860696853492</v>
       </c>
       <c r="C14" t="n">
-        <v>6.515952899906281</v>
+        <v>6.241308939712753</v>
       </c>
       <c r="D14" t="n">
-        <v>7.543433153617502e-17</v>
+        <v>-5.246944431447658e-17</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2429231735496986</v>
+        <v>-0.2531860696853492</v>
       </c>
       <c r="F14" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G14" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="15">
@@ -780,22 +780,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-2.841822193737443</v>
+        <v>-2.830051435678058</v>
       </c>
       <c r="C15" t="n">
-        <v>2.605521880034987</v>
+        <v>2.562281479284375</v>
       </c>
       <c r="D15" t="n">
-        <v>1.180182283711125e-16</v>
+        <v>-1.642521735061875e-16</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7897405221108432</v>
+        <v>0.7648371742968976</v>
       </c>
       <c r="F15" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G15" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029134</v>
       </c>
     </row>
     <row r="16">
@@ -805,22 +805,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.7616206719986545</v>
+        <v>-0.7741510599881057</v>
       </c>
       <c r="C16" t="n">
-        <v>3.216791425024728</v>
+        <v>3.200391524917861</v>
       </c>
       <c r="D16" t="n">
-        <v>2.083569237995157e-17</v>
+        <v>-3.421920281378907e-17</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7616206719986545</v>
+        <v>-0.7741510599881057</v>
       </c>
       <c r="F16" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G16" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="17">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-3.514951815977729</v>
+        <v>-3.514190702959939</v>
       </c>
       <c r="C17" t="n">
-        <v>6.294997338292252</v>
+        <v>6.264426905276412</v>
       </c>
       <c r="D17" t="n">
-        <v>2.141361669414001e-16</v>
+        <v>-2.737536225103126e-17</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1637791168735145</v>
+        <v>0.152790900128693</v>
       </c>
       <c r="F17" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G17" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="18">
@@ -855,22 +855,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-7.975078122202384</v>
+        <v>-8.238533372433395</v>
       </c>
       <c r="C18" t="n">
-        <v>7.559863578251679</v>
+        <v>7.843865217684576</v>
       </c>
       <c r="D18" t="n">
-        <v>-7.458265359947627e-16</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2076072719753528</v>
+        <v>-0.1973340773744095</v>
       </c>
       <c r="F18" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G18" t="n">
-        <v>1.000685400959562</v>
+        <v>1.000856898029134</v>
       </c>
     </row>
     <row r="19">
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-2.780469339451636</v>
+        <v>-2.787855498681763</v>
       </c>
       <c r="C19" t="n">
-        <v>4.604888881772236</v>
+        <v>4.584707269152878</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0220135240385e-16</v>
+        <v>1.09501449004125e-16</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3186832657103453</v>
+        <v>-0.3303345760702164</v>
       </c>
       <c r="F19" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G19" t="n">
-        <v>1.000685400959562</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="20">
@@ -905,22 +905,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.9512264882332893</v>
+        <v>-0.9757566742154179</v>
       </c>
       <c r="C20" t="n">
-        <v>3.703937778204484</v>
+        <v>3.772925806966282</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.866731066850001e-18</v>
+        <v>-4.258389683493751e-17</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6004949339126351</v>
+        <v>0.6071374861784822</v>
       </c>
       <c r="F20" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G20" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="21">
@@ -930,22 +930,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-2.365439947036252</v>
+        <v>-2.355716144368795</v>
       </c>
       <c r="C21" t="n">
-        <v>2.988889235402396</v>
+        <v>2.930501831851672</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2166827667125e-16</v>
+        <v>8.554800703447268e-17</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3117246441830721</v>
+        <v>0.2873928437414381</v>
       </c>
       <c r="F21" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G21" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="22">
@@ -955,22 +955,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-2.212962983088507</v>
+        <v>-2.199502349712417</v>
       </c>
       <c r="C22" t="n">
-        <v>4.421526004152803</v>
+        <v>4.339189289776204</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2166827667125e-17</v>
+        <v>-1.034180351705625e-16</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03284429044874903</v>
+        <v>0.01157144516402429</v>
       </c>
       <c r="F22" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G22" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="23">
@@ -980,22 +980,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.9467014684878265</v>
+        <v>-0.9396395438469278</v>
       </c>
       <c r="C23" t="n">
-        <v>1.655682038412637</v>
+        <v>1.665433170938654</v>
       </c>
       <c r="D23" t="n">
-        <v>1.460019320055e-17</v>
+        <v>-1.612104665894063e-16</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9467014684878265</v>
+        <v>-0.9396395438469278</v>
       </c>
       <c r="F23" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G23" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="24">
@@ -1005,22 +1005,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.072916474962699</v>
+        <v>-1.095131419551467</v>
       </c>
       <c r="C24" t="n">
-        <v>1.857985397808924</v>
+        <v>1.838100949285544</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.104861186412626e-16</v>
+        <v>2.129194841746875e-17</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4413151134872422</v>
+        <v>0.4378583307974893</v>
       </c>
       <c r="F24" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G24" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="25">
@@ -1030,22 +1030,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.4042442108783149</v>
+        <v>-0.4021861793845504</v>
       </c>
       <c r="C25" t="n">
-        <v>3.253174886581788</v>
+        <v>3.257758549594442</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.676702086767501e-17</v>
+        <v>7.908437983631252e-17</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4042442108783149</v>
+        <v>-0.4021861793845504</v>
       </c>
       <c r="F25" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G25" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="26">
@@ -1055,22 +1055,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1285214274886148</v>
+        <v>-0.127701024055796</v>
       </c>
       <c r="C26" t="n">
-        <v>9.22041485120967</v>
+        <v>9.289992452870829</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.866731066850001e-18</v>
+        <v>1.520853458390625e-18</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1285214274886148</v>
+        <v>-0.127701024055796</v>
       </c>
       <c r="F26" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G26" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="27">
@@ -1080,22 +1080,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2927694190084836</v>
+        <v>-0.2878825621456251</v>
       </c>
       <c r="C27" t="n">
-        <v>4.110032180254794</v>
+        <v>4.176132075968726</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.440892098500626e-17</v>
+        <v>2.737536225103126e-17</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2927694190084836</v>
+        <v>-0.2878825621456251</v>
       </c>
       <c r="F27" t="n">
-        <v>1.000342641778086</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G27" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029134</v>
       </c>
     </row>
     <row r="28">
@@ -1105,22 +1105,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.06939258050999438</v>
+        <v>-0.07763000441188135</v>
       </c>
       <c r="C28" t="n">
-        <v>14.99281765578674</v>
+        <v>13.4025367627311</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.92003864011e-17</v>
+        <v>-6.083413833562501e-18</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.06939258050999438</v>
+        <v>-0.07763000441188135</v>
       </c>
       <c r="F28" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G28" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="29">
@@ -1130,22 +1130,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1904814736846831</v>
+        <v>-0.1664233792932206</v>
       </c>
       <c r="C29" t="n">
-        <v>7.682057447498138</v>
+        <v>8.640189107693288</v>
       </c>
       <c r="D29" t="n">
-        <v>-3.406711746795001e-17</v>
+        <v>-2.129194841746875e-17</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1904814736846831</v>
+        <v>-0.1664233792932206</v>
       </c>
       <c r="F29" t="n">
-        <v>1.000342641778086</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G29" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="30">
@@ -1155,22 +1155,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.208604423534465</v>
+        <v>-1.179920945287459</v>
       </c>
       <c r="C30" t="n">
-        <v>3.288781152496332</v>
+        <v>3.320261107511464</v>
       </c>
       <c r="D30" t="n">
-        <v>5.110067620192501e-17</v>
+        <v>8.820950058665627e-17</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.05118901793830374</v>
+        <v>-0.07142021904654809</v>
       </c>
       <c r="F30" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G30" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="31">
@@ -1180,22 +1180,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.112339552660391</v>
+        <v>-1.085456172774963</v>
       </c>
       <c r="C31" t="n">
-        <v>1.795650921645751</v>
+        <v>1.777409556644367</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.2166827667125e-17</v>
+        <v>-4.106304337654688e-17</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4338084419889573</v>
+        <v>-0.4546552493435852</v>
       </c>
       <c r="F31" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G31" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="32">
@@ -1205,22 +1205,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.109798062474761</v>
+        <v>-1.080042826903726</v>
       </c>
       <c r="C32" t="n">
-        <v>3.180223794843607</v>
+        <v>3.199719763385124</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.859204501774376e-17</v>
+        <v>-7.376139273194533e-17</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1675970003534375</v>
+        <v>-0.240089421333017</v>
       </c>
       <c r="F32" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G32" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029134</v>
       </c>
     </row>
     <row r="33">
@@ -1230,22 +1230,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.367654733107055</v>
+        <v>-1.277870490842456</v>
       </c>
       <c r="C33" t="n">
-        <v>1.645209711006642</v>
+        <v>1.52066588410237</v>
       </c>
       <c r="D33" t="n">
-        <v>3.567435540277722e-14</v>
+        <v>-6.988625811996601e-14</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1387774889497933</v>
+        <v>-0.345025032527514</v>
       </c>
       <c r="F33" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G33" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="34">
@@ -1255,22 +1255,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-6.361593505175152</v>
+        <v>-6.273704272931609</v>
       </c>
       <c r="C34" t="n">
-        <v>5.00544702298796</v>
+        <v>4.921303991881365</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.418043764603419e-15</v>
+        <v>-2.555033810096251e-15</v>
       </c>
       <c r="E34" t="n">
-        <v>0.03446994549377981</v>
+        <v>0.03822187004760091</v>
       </c>
       <c r="F34" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G34" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="35">
@@ -1280,22 +1280,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.541932106739068</v>
+        <v>-1.533653561228353</v>
       </c>
       <c r="C35" t="n">
-        <v>4.826443779651425</v>
+        <v>4.791584290165417</v>
       </c>
       <c r="D35" t="n">
-        <v>2.567200637763375e-16</v>
+        <v>-2.524616740928438e-16</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.2682569294609691</v>
+        <v>-0.2686059909495987</v>
       </c>
       <c r="F35" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G35" t="n">
-        <v>1.000685400959562</v>
+        <v>1.000856898029134</v>
       </c>
     </row>
     <row r="36">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-2.048330799186041</v>
+        <v>-2.031704909597648</v>
       </c>
       <c r="C36" t="n">
-        <v>1.294621051308918</v>
+        <v>1.294224244626375</v>
       </c>
       <c r="D36" t="n">
-        <v>1.070680834707e-16</v>
+        <v>2.250863118418126e-16</v>
       </c>
       <c r="E36" t="n">
-        <v>0.412810967265625</v>
+        <v>0.4139891693242135</v>
       </c>
       <c r="F36" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G36" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="37">
@@ -1330,22 +1330,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-3.363038893116097</v>
+        <v>-3.362836100949858</v>
       </c>
       <c r="C37" t="n">
-        <v>3.863104357408187</v>
+        <v>3.844321451714829</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.87369146073725e-15</v>
+        <v>-2.749703052770251e-15</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.006981842319383289</v>
+        <v>-0.003957466298867491</v>
       </c>
       <c r="F37" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G37" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029134</v>
       </c>
     </row>
     <row r="38">
@@ -1355,22 +1355,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.793919398933742</v>
+        <v>-1.772453026293848</v>
       </c>
       <c r="C38" t="n">
-        <v>5.912391734020543</v>
+        <v>5.798491778667644</v>
       </c>
       <c r="D38" t="n">
-        <v>-6.083413833562501e-17</v>
+        <v>-7.908437983631252e-17</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.2048290518243997</v>
+        <v>-0.2232637833718904</v>
       </c>
       <c r="F38" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G38" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="39">
@@ -1380,22 +1380,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-6.271177421017662</v>
+        <v>-6.194536881618625</v>
       </c>
       <c r="C39" t="n">
-        <v>3.668021063152571</v>
+        <v>3.598845276069442</v>
       </c>
       <c r="D39" t="n">
-        <v>3.248542987122376e-16</v>
+        <v>-5.368612708118908e-16</v>
       </c>
       <c r="E39" t="n">
-        <v>0.07017578565671938</v>
+        <v>0.06544203969070374</v>
       </c>
       <c r="F39" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G39" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
     <row r="40">
@@ -1405,22 +1405,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-5.714683694835959</v>
+        <v>-5.76331784317661</v>
       </c>
       <c r="C40" t="n">
-        <v>4.326976433010307</v>
+        <v>4.347694623170339</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.652368431433251e-16</v>
+        <v>4.866731066850001e-17</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1921752038971382</v>
+        <v>0.1843365487921836</v>
       </c>
       <c r="F40" t="n">
-        <v>1.000342641778087</v>
+        <v>1.000428357269592</v>
       </c>
       <c r="G40" t="n">
-        <v>1.000685400959561</v>
+        <v>1.000856898029135</v>
       </c>
     </row>
   </sheetData>
